--- a/data/trans_bre/IP13-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP13-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>-0,15</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>-3,29%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 6,25</t>
+          <t>-2,33; 5,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 6,18</t>
+          <t>-2,84; 6,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 3,41</t>
+          <t>-3,97; 3,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 4,56</t>
+          <t>-5,03; 4,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-47,84; 294,37</t>
+          <t>-49,97; 250,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,49; 207,28</t>
+          <t>-51,22; 217,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-78,54; 283,55</t>
+          <t>-79,5; 223,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-65,64; 185,4</t>
+          <t>-69,47; 176,93</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>-6,35%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 2,95</t>
+          <t>-4,57; 2,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 4,92</t>
+          <t>-2,41; 4,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 4,37</t>
+          <t>-2,6; 4,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 3,96</t>
+          <t>-3,82; 3,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,11; 84,02</t>
+          <t>-56,61; 58,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 153,54</t>
+          <t>-35,21; 136,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,05; 133,73</t>
+          <t>-39,9; 121,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,04; 105,18</t>
+          <t>-54,32; 80,74</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-19,41%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 5,42</t>
+          <t>-2,87; 5,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 0,16</t>
+          <t>-8,93; -0,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 4,17</t>
+          <t>-4,21; 4,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 3,01</t>
+          <t>-5,11; 5,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,78; 142,77</t>
+          <t>-40,74; 172,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-78,08; 5,75</t>
+          <t>-75,54; 3,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-49,96; 99,07</t>
+          <t>-50,38; 119,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-66,03; 55,92</t>
+          <t>-50,47; 99,71</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,21</t>
+          <t>-2,41</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-27,06%</t>
+          <t>-29,58%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,55; -0,16</t>
+          <t>-6,05; -0,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 2,74</t>
+          <t>-5,12; 2,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 5,74</t>
+          <t>-0,72; 5,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 2,7</t>
+          <t>-7,08; 2,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-90,44; 6,4</t>
+          <t>-88,97; 10,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,71; 78,6</t>
+          <t>-66,25; 73,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 344,96</t>
+          <t>-27,47; 319,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,02; 52,41</t>
+          <t>-66,27; 46,24</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-0,67</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-11,53%</t>
+          <t>-10,25%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,5</t>
+          <t>-2,21; 1,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 1,51</t>
+          <t>-2,57; 1,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,77</t>
+          <t>-0,82; 2,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,56</t>
+          <t>-2,79; 1,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,17; 36,7</t>
+          <t>-38,22; 31,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-37,72; 29,79</t>
+          <t>-36,97; 31,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 78,47</t>
+          <t>-17,21; 74,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-40,14; 29,18</t>
+          <t>-36,81; 32,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP13-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP13-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,54</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,5</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>39,04%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>31,43%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-6,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-3,29%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.541958573143979</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.502396708930911</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.1973127025452437</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.1541372038425429</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.3903569464109624</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.3142559647934041</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.06120715328073244</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.03287036937531404</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-2,33; 5,77</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-2,84; 6,4</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-3,97; 3,2</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-5,03; 4,28</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-49,97; 250,08</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-51,22; 217,19</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-79,5; 223,17</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-69,47; 176,93</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.331321323963851</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.84272527449615</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.970802869549288</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-5.030071237307511</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.4996867860915064</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.5122230882440779</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.794960177376036</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.6947278748924007</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.769252930246009</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.401324245367281</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.204357582472422</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.280585607213637</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.500837879708472</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2.171885733409849</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>2.231731129025969</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.769311325156482</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,86</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,06</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-14,35%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>19,99%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,6%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-6,35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-4,57; 2,42</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,41; 4,7</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,6; 4,08</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,82; 3,17</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-56,61; 58,88</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-35,21; 136,48</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-39,9; 121,22</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-54,32; 80,74</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.8551412081011109</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.059245294054415</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.7034609546305568</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.3530615197903805</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1435434801283424</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1999483704987464</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.136032800240105</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.06345363901683873</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-4,45</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>24,42%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-48,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-4.57039904062243</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.40948177717172</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.602162091731979</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.818255423164327</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5661366026986</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3521041775673334</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3990203628058127</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.5432108484429329</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,87; 5,83</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-8,93; -0,49</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,21; 4,3</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-5,11; 5,21</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-40,74; 172,69</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-75,54; 3,96</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-50,38; 119,63</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-50,47; 99,71</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.418255293086153</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.699393452928958</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.083435440736335</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.166547537368875</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.5888315455385102</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.364811178649525</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.212183550264134</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.8074087327678865</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-2,79</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,14</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,41</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-60,9%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-20,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>75,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-29,58%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.294130660600835</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-4.445287434103426</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1205593928875752</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.1617172437280323</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.2442142164550503</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.4808811067091795</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.01960925580439537</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.02136078655885603</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-6,05; -0,13</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,12; 2,61</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,72; 5,8</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-7,08; 2,37</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-88,97; 10,28</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-66,25; 73,41</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-27,47; 319,51</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-66,27; 46,24</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.873399778068703</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-8.927057124409158</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.211598980143974</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.105296224842022</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.4073656054920788</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.7553774249790264</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.5038333370933552</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.504718580552838</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.831123137258596</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-0.4888766089602729</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.30401392501694</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.214532339147826</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.726946629028182</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.03956726309893024</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.19626744007057</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.9970845585121353</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-2.787895144874469</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.141944000849124</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.290135096610573</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.411843925280571</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.6089704682594854</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2040397280246763</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.7523072245667259</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.2957892948515758</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-6.047596392968233</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.12349912608546</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.7249227015052064</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-7.081041477269344</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.8896509573760834</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6625163015801409</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2746685456670656</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.662694484047667</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-0.1258409146772143</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.614802577097451</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.804778095022741</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.370880717761388</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1027918455194356</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.7340590676769828</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>3.195071299779841</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.4623782607814211</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-10,68%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-11,47%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,18%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-10,25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,21; 1,39</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,57; 1,56</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,82; 2,67</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,79; 1,56</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-38,22; 31,18</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-36,97; 31,39</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-17,21; 74,36</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-36,81; 32,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.5338567381889356</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.7048840110966369</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.8470050451875599</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.6678565578777579</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1067871401302399</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.1147433242969344</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.1918416343656075</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.1024911637082304</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.205227485683008</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.572878316298493</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.8196046135442451</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.791152072450807</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3821864894552733</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3697011060122253</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1720618312356546</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3680765240228403</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.393326958762928</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.564670611426898</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.672001923249898</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.557089109063349</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.3118324419498923</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.3139403295422819</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.7435611600403741</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.3199894896356457</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
